--- a/Config/Excel/Tables/角色表.xlsx
+++ b/Config/Excel/Tables/角色表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="26640" windowHeight="6975"/>
+    <workbookView windowWidth="28560" windowHeight="4560"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -100,7 +100,7 @@
     <t>带有强力攻击技能</t>
   </si>
   <si>
-    <t>Ellen</t>
+    <t>Player</t>
   </si>
 </sst>
 </file>

--- a/Config/Excel/Tables/角色表.xlsx
+++ b/Config/Excel/Tables/角色表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28560" windowHeight="4560"/>
+    <workbookView windowWidth="25440" windowHeight="8700"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="26">
   <si>
     <t>##var</t>
   </si>
@@ -61,6 +61,9 @@
     <t>Prefab</t>
   </si>
   <si>
+    <t>SkillSetId</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -92,6 +95,9 @@
   </si>
   <si>
     <t>模型预制体</t>
+  </si>
+  <si>
+    <t>技能组id</t>
   </si>
   <si>
     <t>米克尔</t>
@@ -1068,13 +1074,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="10" max="10" width="8.875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1105,42 +1112,48 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="H2" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:11">
       <c r="A3" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>1</v>
@@ -1149,28 +1162,31 @@
         <v>2</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="K3" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="4" ht="28.5" spans="1:10">
+    <row r="4" ht="28.5" spans="1:11">
       <c r="B4">
         <v>1</v>
       </c>
@@ -1178,10 +1194,10 @@
         <v>1001</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F4" s="4">
         <v>1</v>
@@ -1196,10 +1212,13 @@
         <v>68</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:11">
       <c r="D5" s="4"/>
       <c r="E5" s="5"/>
       <c r="F5" s="4"/>
@@ -1207,7 +1226,7 @@
       <c r="H5" s="4"/>
       <c r="I5" s="4"/>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:11">
       <c r="D6" s="4"/>
       <c r="E6" s="5"/>
       <c r="F6" s="4"/>
@@ -1216,7 +1235,7 @@
       <c r="I6" s="4"/>
       <c r="J6" s="6"/>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:11">
       <c r="D7" s="4"/>
       <c r="E7" s="5"/>
       <c r="F7" s="4"/>
@@ -1225,7 +1244,7 @@
       <c r="I7" s="4"/>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:11">
       <c r="D8" s="4"/>
       <c r="E8" s="5"/>
       <c r="F8" s="4"/>
@@ -1234,7 +1253,7 @@
       <c r="I8" s="4"/>
       <c r="J8" s="4"/>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:11">
       <c r="J9" s="4"/>
     </row>
   </sheetData>

--- a/Config/Excel/Tables/角色表.xlsx
+++ b/Config/Excel/Tables/角色表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25440" windowHeight="8700"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="32">
   <si>
     <t>##var</t>
   </si>
@@ -64,6 +64,12 @@
     <t>SkillSetId</t>
   </si>
   <si>
+    <t>MoveAsset</t>
+  </si>
+  <si>
+    <t>JumpAsset</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -100,6 +106,12 @@
     <t>技能组id</t>
   </si>
   <si>
+    <t>idle和移动动画资源</t>
+  </si>
+  <si>
+    <t>跳跃动画资源</t>
+  </si>
+  <si>
     <t>米克尔</t>
   </si>
   <si>
@@ -107,6 +119,12 @@
   </si>
   <si>
     <t>Player</t>
+  </si>
+  <si>
+    <t>PlayerMove1</t>
+  </si>
+  <si>
+    <t>PlayerJump1</t>
   </si>
 </sst>
 </file>
@@ -747,7 +765,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -756,6 +774,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1074,14 +1095,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="10" max="10" width="8.875" style="1" customWidth="1"/>
     <col min="11" max="11" width="11.5" customWidth="1"/>
+    <col min="12" max="12" width="19.5" customWidth="1"/>
+    <col min="13" max="13" width="12.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1115,45 +1138,57 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
+      <c r="L1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:13">
       <c r="A2" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K2" t="s">
-        <v>12</v>
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:13">
       <c r="A3" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>1</v>
@@ -1162,99 +1197,141 @@
         <v>2</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K3" t="s">
-        <v>22</v>
+        <v>24</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="M3" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="4" ht="28.5" spans="1:11">
+    <row r="4" ht="28.5" spans="1:13">
       <c r="B4">
         <v>1</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="5">
         <v>1001</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F4" s="4">
+      <c r="D4" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" s="5">
         <v>1</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G4" s="5">
         <v>1</v>
       </c>
-      <c r="H4" s="4">
+      <c r="H4" s="5">
         <v>178</v>
       </c>
-      <c r="I4" s="4">
+      <c r="I4" s="5">
         <v>68</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="K4">
         <v>1</v>
       </c>
+      <c r="L4" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>31</v>
+      </c>
     </row>
-    <row r="5" spans="1:11">
-      <c r="D5" s="4"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
+    <row r="5" ht="28.5" spans="1:13">
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5" s="5">
+        <v>1001</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" s="5">
+        <v>1</v>
+      </c>
+      <c r="G5" s="5">
+        <v>1</v>
+      </c>
+      <c r="H5" s="5">
+        <v>178</v>
+      </c>
+      <c r="I5" s="5">
+        <v>68</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>31</v>
+      </c>
     </row>
-    <row r="6" spans="1:11">
-      <c r="D6" s="4"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="6"/>
+    <row r="6" spans="1:13">
+      <c r="D6" s="5"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="7"/>
     </row>
-    <row r="7" spans="1:11">
-      <c r="D7" s="4"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="6"/>
+    <row r="7" spans="1:13">
+      <c r="D7" s="5"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="7"/>
     </row>
-    <row r="8" spans="1:11">
-      <c r="D8" s="4"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
+    <row r="8" spans="1:13">
+      <c r="D8" s="5"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
     </row>
-    <row r="9" spans="1:11">
-      <c r="J9" s="4"/>
+    <row r="9" spans="1:13">
+      <c r="J9" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
